--- a/purchase_order_generator/templates/input_template.xlsx
+++ b/purchase_order_generator/templates/input_template.xlsx
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="189">
   <si>
     <t>款号</t>
   </si>
@@ -714,6 +714,12 @@
   </si>
   <si>
     <t>温馨提示卡片</t>
+  </si>
+  <si>
+    <t>采购仓库</t>
+  </si>
+  <si>
+    <t>启创-福茂仓库</t>
   </si>
 </sst>
 </file>
@@ -5170,7 +5176,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5207,6 +5213,14 @@
       </c>
       <c r="B4" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/purchase_order_generator/templates/input_template.xlsx
+++ b/purchase_order_generator/templates/input_template.xlsx
@@ -5224,6 +5224,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" showInputMessage="1">
+      <formula1>"启创-利得仓库,启创-福茂仓库,启创-立祥仓库A区,启创-立祥仓库B区"</formula1>
+      <sqref>B5</sqref>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/purchase_order_generator/templates/input_template.xlsx
+++ b/purchase_order_generator/templates/input_template.xlsx
@@ -5225,9 +5225,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" showInputMessage="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" showInputMessage="1" sqref="B5">
       <formula1>"启创-利得仓库,启创-福茂仓库,启创-立祥仓库A区,启创-立祥仓库B区"</formula1>
-      <sqref>B5</sqref>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/purchase_order_generator/templates/input_template.xlsx
+++ b/purchase_order_generator/templates/input_template.xlsx
@@ -1740,9 +1740,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1753,11 +1753,13 @@
     <col min="6" max="6" width="9" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1785,7 +1787,17 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1848,7 +1860,7 @@
       <c r="I3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>19</v>
       </c>
     </row>
